--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -2284,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187625</v>
+        <v>131187616</v>
       </c>
       <c r="B16" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,19 +2295,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2315,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441119</v>
+        <v>441123</v>
       </c>
       <c r="R16" t="n">
-        <v>7057196</v>
+        <v>7057208</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,6 +2355,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,7 +2386,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131187616</v>
+        <v>131187611</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2412,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441123</v>
+        <v>440913</v>
       </c>
       <c r="R17" t="n">
-        <v>7057208</v>
+        <v>7056941</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2461,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187611</v>
+        <v>131187625</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,23 +2499,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2514,10 +2519,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440913</v>
+        <v>441119</v>
       </c>
       <c r="R18" t="n">
-        <v>7056941</v>
+        <v>7057196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2550,11 +2555,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -2284,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187616</v>
+        <v>131187625</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,23 +2295,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2319,10 +2315,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441123</v>
+        <v>441119</v>
       </c>
       <c r="R16" t="n">
-        <v>7057208</v>
+        <v>7057196</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,11 +2351,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,7 +2377,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131187611</v>
+        <v>131187616</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2421,10 +2412,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440913</v>
+        <v>441123</v>
       </c>
       <c r="R17" t="n">
-        <v>7056941</v>
+        <v>7057208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2452,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187625</v>
+        <v>131187611</v>
       </c>
       <c r="B18" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2499,19 +2490,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2519,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441119</v>
+        <v>440913</v>
       </c>
       <c r="R18" t="n">
-        <v>7057196</v>
+        <v>7056941</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,6 +2550,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -2377,7 +2377,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131187616</v>
+        <v>131187611</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441123</v>
+        <v>440913</v>
       </c>
       <c r="R17" t="n">
-        <v>7057208</v>
+        <v>7056941</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,7 +2479,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187611</v>
+        <v>131187616</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440913</v>
+        <v>441123</v>
       </c>
       <c r="R18" t="n">
-        <v>7056941</v>
+        <v>7057208</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,7 +2683,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131187621</v>
+        <v>131187613</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441121</v>
+        <v>441028</v>
       </c>
       <c r="R20" t="n">
-        <v>7056920</v>
+        <v>7056998</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187613</v>
+        <v>131187621</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441028</v>
+        <v>441121</v>
       </c>
       <c r="R21" t="n">
-        <v>7056998</v>
+        <v>7056920</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>131154933</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131154932</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>131187626</v>
       </c>
       <c r="B10" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131187625</v>
       </c>
       <c r="B16" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131187611</v>
+        <v>131187616</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440913</v>
+        <v>441123</v>
       </c>
       <c r="R17" t="n">
-        <v>7056941</v>
+        <v>7057208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,7 +2479,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187616</v>
+        <v>131187611</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441123</v>
+        <v>440913</v>
       </c>
       <c r="R18" t="n">
-        <v>7057208</v>
+        <v>7056941</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2683,7 +2683,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131187613</v>
+        <v>131187621</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441028</v>
+        <v>441121</v>
       </c>
       <c r="R20" t="n">
-        <v>7056998</v>
+        <v>7056920</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187621</v>
+        <v>131187613</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441121</v>
+        <v>441028</v>
       </c>
       <c r="R21" t="n">
-        <v>7056920</v>
+        <v>7056998</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2992,7 +2992,7 @@
         <v>131187600</v>
       </c>
       <c r="B23" t="n">
-        <v>92531</v>
+        <v>92532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -1681,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131187626</v>
+        <v>131187615</v>
       </c>
       <c r="B10" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,19 +1692,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1712,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441180</v>
+        <v>441121</v>
       </c>
       <c r="R10" t="n">
-        <v>7057056</v>
+        <v>7057222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,6 +1752,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,7 +1783,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131187615</v>
+        <v>131187619</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1809,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441121</v>
+        <v>441118</v>
       </c>
       <c r="R11" t="n">
-        <v>7057222</v>
+        <v>7056975</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,7 +1885,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187619</v>
+        <v>131187614</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -1911,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441118</v>
+        <v>441097</v>
       </c>
       <c r="R12" t="n">
-        <v>7056975</v>
+        <v>7057228</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,7 +1960,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187614</v>
+        <v>131187626</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>91833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,23 +1998,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2013,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441097</v>
+        <v>441180</v>
       </c>
       <c r="R13" t="n">
-        <v>7057228</v>
+        <v>7057056</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,11 +2054,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2287,7 +2287,7 @@
         <v>131187625</v>
       </c>
       <c r="B16" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>131187600</v>
       </c>
       <c r="B23" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>131154933</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131154932</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131187615</v>
+        <v>131187626</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,23 +1692,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,10 +1712,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441121</v>
+        <v>441180</v>
       </c>
       <c r="R10" t="n">
-        <v>7057222</v>
+        <v>7057056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1752,11 +1748,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,7 +1774,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131187619</v>
+        <v>131187615</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1818,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441118</v>
+        <v>441121</v>
       </c>
       <c r="R11" t="n">
-        <v>7056975</v>
+        <v>7057222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1885,7 +1876,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187614</v>
+        <v>131187619</v>
       </c>
       <c r="B12" t="n">
         <v>57884</v>
@@ -1920,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441097</v>
+        <v>441118</v>
       </c>
       <c r="R12" t="n">
-        <v>7057228</v>
+        <v>7056975</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1960,7 +1951,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187626</v>
+        <v>131187614</v>
       </c>
       <c r="B13" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,19 +1989,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2018,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441180</v>
+        <v>441097</v>
       </c>
       <c r="R13" t="n">
-        <v>7057056</v>
+        <v>7057228</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,6 +2049,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2287,7 +2287,7 @@
         <v>131187625</v>
       </c>
       <c r="B16" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>131187600</v>
       </c>
       <c r="B23" t="n">
-        <v>92535</v>
+        <v>92536</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154924</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154923</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154925</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>131154926</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131154933</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131154932</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131187612</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>131187623</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>131187626</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>131187615</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>131187619</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>131187614</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>131187620</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131187617</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131187625</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>131187616</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>131187611</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>131187622</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>131187621</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>131187613</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>131187618</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>131187600</v>
       </c>
       <c r="B23" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154924</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154923</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154925</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>131154926</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131154933</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131154932</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131187612</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>131187623</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>131187626</v>
       </c>
       <c r="B10" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>131187615</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>131187619</v>
       </c>
       <c r="B12" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>131187614</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>131187620</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131187617</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131187625</v>
       </c>
       <c r="B16" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>131187616</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>131187611</v>
       </c>
       <c r="B18" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>131187622</v>
       </c>
       <c r="B19" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>131187621</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>131187613</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>131187618</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>131187600</v>
       </c>
       <c r="B23" t="n">
-        <v>92538</v>
+        <v>92539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -1681,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131187626</v>
+        <v>131187615</v>
       </c>
       <c r="B10" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,19 +1692,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1712,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441180</v>
+        <v>441121</v>
       </c>
       <c r="R10" t="n">
-        <v>7057056</v>
+        <v>7057222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,6 +1752,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,7 +1783,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131187615</v>
+        <v>131187619</v>
       </c>
       <c r="B11" t="n">
         <v>57887</v>
@@ -1809,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441121</v>
+        <v>441118</v>
       </c>
       <c r="R11" t="n">
-        <v>7057222</v>
+        <v>7056975</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,7 +1885,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187619</v>
+        <v>131187614</v>
       </c>
       <c r="B12" t="n">
         <v>57887</v>
@@ -1911,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441118</v>
+        <v>441097</v>
       </c>
       <c r="R12" t="n">
-        <v>7056975</v>
+        <v>7057228</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,7 +1960,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187614</v>
+        <v>131187626</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,23 +1998,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2013,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441097</v>
+        <v>441180</v>
       </c>
       <c r="R13" t="n">
-        <v>7057228</v>
+        <v>7057056</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,11 +2054,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2284,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187625</v>
+        <v>131187616</v>
       </c>
       <c r="B16" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,19 +2295,23 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2315,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441119</v>
+        <v>441123</v>
       </c>
       <c r="R16" t="n">
-        <v>7057196</v>
+        <v>7057208</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,6 +2355,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,7 +2386,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131187616</v>
+        <v>131187611</v>
       </c>
       <c r="B17" t="n">
         <v>57887</v>
@@ -2412,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441123</v>
+        <v>440913</v>
       </c>
       <c r="R17" t="n">
-        <v>7057208</v>
+        <v>7056941</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2461,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187611</v>
+        <v>131187625</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,23 +2499,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2514,10 +2519,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440913</v>
+        <v>441119</v>
       </c>
       <c r="R18" t="n">
-        <v>7056941</v>
+        <v>7057196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2550,11 +2555,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -1681,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131187615</v>
+        <v>131187626</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,23 +1692,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,10 +1712,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441121</v>
+        <v>441180</v>
       </c>
       <c r="R10" t="n">
-        <v>7057222</v>
+        <v>7057056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1752,11 +1748,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,7 +1774,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131187619</v>
+        <v>131187615</v>
       </c>
       <c r="B11" t="n">
         <v>57887</v>
@@ -1818,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441118</v>
+        <v>441121</v>
       </c>
       <c r="R11" t="n">
-        <v>7056975</v>
+        <v>7057222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1885,7 +1876,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187614</v>
+        <v>131187619</v>
       </c>
       <c r="B12" t="n">
         <v>57887</v>
@@ -1920,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441097</v>
+        <v>441118</v>
       </c>
       <c r="R12" t="n">
-        <v>7057228</v>
+        <v>7056975</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1960,7 +1951,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187626</v>
+        <v>131187614</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,19 +1989,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2018,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441180</v>
+        <v>441097</v>
       </c>
       <c r="R13" t="n">
-        <v>7057056</v>
+        <v>7057228</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,6 +2049,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154924</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154923</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154925</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>131154926</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131154933</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131154932</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131187612</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>131187623</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131187626</v>
+        <v>131187615</v>
       </c>
       <c r="B10" t="n">
-        <v>91837</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,19 +1692,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1712,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441180</v>
+        <v>441121</v>
       </c>
       <c r="R10" t="n">
-        <v>7057056</v>
+        <v>7057222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,6 +1752,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131187615</v>
+        <v>131187619</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441121</v>
+        <v>441118</v>
       </c>
       <c r="R11" t="n">
-        <v>7057222</v>
+        <v>7056975</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,10 +1885,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187619</v>
+        <v>131187614</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441118</v>
+        <v>441097</v>
       </c>
       <c r="R12" t="n">
-        <v>7056975</v>
+        <v>7057228</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,7 +1960,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187614</v>
+        <v>131187626</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,23 +1998,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2013,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441097</v>
+        <v>441180</v>
       </c>
       <c r="R13" t="n">
-        <v>7057228</v>
+        <v>7057056</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,11 +2054,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,7 +2083,7 @@
         <v>131187620</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131187617</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131187616</v>
+        <v>131187625</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,23 +2295,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2319,10 +2315,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441123</v>
+        <v>441119</v>
       </c>
       <c r="R16" t="n">
-        <v>7057208</v>
+        <v>7057196</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,11 +2351,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2377,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131187611</v>
+        <v>131187616</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2421,10 +2412,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440913</v>
+        <v>441123</v>
       </c>
       <c r="R17" t="n">
-        <v>7056941</v>
+        <v>7057208</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2452,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131187625</v>
+        <v>131187611</v>
       </c>
       <c r="B18" t="n">
-        <v>91837</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2499,19 +2490,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2519,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441119</v>
+        <v>440913</v>
       </c>
       <c r="R18" t="n">
-        <v>7057196</v>
+        <v>7056941</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2555,6 +2550,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,7 +2584,7 @@
         <v>131187622</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131187621</v>
+        <v>131187613</v>
       </c>
       <c r="B20" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441121</v>
+        <v>441028</v>
       </c>
       <c r="R20" t="n">
-        <v>7056920</v>
+        <v>7056998</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187613</v>
+        <v>131187621</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441028</v>
+        <v>441121</v>
       </c>
       <c r="R21" t="n">
-        <v>7056998</v>
+        <v>7056920</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
         <v>131187618</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>131187600</v>
       </c>
       <c r="B23" t="n">
-        <v>92539</v>
+        <v>92540</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -1681,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131187615</v>
+        <v>131187626</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,23 +1692,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,10 +1712,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441121</v>
+        <v>441180</v>
       </c>
       <c r="R10" t="n">
-        <v>7057222</v>
+        <v>7057056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1752,11 +1748,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,7 +1774,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131187619</v>
+        <v>131187615</v>
       </c>
       <c r="B11" t="n">
         <v>57888</v>
@@ -1818,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441118</v>
+        <v>441121</v>
       </c>
       <c r="R11" t="n">
-        <v>7056975</v>
+        <v>7057222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1885,7 +1876,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187614</v>
+        <v>131187619</v>
       </c>
       <c r="B12" t="n">
         <v>57888</v>
@@ -1920,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441097</v>
+        <v>441118</v>
       </c>
       <c r="R12" t="n">
-        <v>7057228</v>
+        <v>7056975</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1960,7 +1951,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187626</v>
+        <v>131187614</v>
       </c>
       <c r="B13" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,19 +1989,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2018,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441180</v>
+        <v>441097</v>
       </c>
       <c r="R13" t="n">
-        <v>7057056</v>
+        <v>7057228</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,6 +2049,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2683,7 +2683,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131187613</v>
+        <v>131187621</v>
       </c>
       <c r="B20" t="n">
         <v>57888</v>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441028</v>
+        <v>441121</v>
       </c>
       <c r="R20" t="n">
-        <v>7056998</v>
+        <v>7056920</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187621</v>
+        <v>131187613</v>
       </c>
       <c r="B21" t="n">
         <v>57888</v>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441121</v>
+        <v>441028</v>
       </c>
       <c r="R21" t="n">
-        <v>7056920</v>
+        <v>7056998</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154924</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154923</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154925</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>131154926</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131154933</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131154932</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131187612</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>131187623</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>131187626</v>
       </c>
       <c r="B10" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>131187615</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>131187619</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>131187614</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>131187620</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131187617</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131187625</v>
       </c>
       <c r="B16" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>131187616</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>131187611</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>131187622</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131187621</v>
+        <v>131187613</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441121</v>
+        <v>441028</v>
       </c>
       <c r="R20" t="n">
-        <v>7056920</v>
+        <v>7056998</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187613</v>
+        <v>131187621</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441028</v>
+        <v>441121</v>
       </c>
       <c r="R21" t="n">
-        <v>7056998</v>
+        <v>7056920</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
         <v>131187618</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>131187600</v>
       </c>
       <c r="B23" t="n">
-        <v>92540</v>
+        <v>92543</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154924</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154923</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154925</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>131154926</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131154933</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131154932</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131187612</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>131187623</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131187626</v>
+        <v>131187615</v>
       </c>
       <c r="B10" t="n">
-        <v>91841</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,19 +1692,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1712,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441180</v>
+        <v>441121</v>
       </c>
       <c r="R10" t="n">
-        <v>7057056</v>
+        <v>7057222</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,6 +1752,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131187615</v>
+        <v>131187619</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441121</v>
+        <v>441118</v>
       </c>
       <c r="R11" t="n">
-        <v>7057222</v>
+        <v>7056975</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1876,10 +1885,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187619</v>
+        <v>131187614</v>
       </c>
       <c r="B12" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441118</v>
+        <v>441097</v>
       </c>
       <c r="R12" t="n">
-        <v>7056975</v>
+        <v>7057228</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,7 +1960,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187614</v>
+        <v>131187626</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>91842</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,23 +1998,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2013,10 +2018,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441097</v>
+        <v>441180</v>
       </c>
       <c r="R13" t="n">
-        <v>7057228</v>
+        <v>7057056</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,11 +2054,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,7 +2083,7 @@
         <v>131187620</v>
       </c>
       <c r="B14" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131187617</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131187625</v>
       </c>
       <c r="B16" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>131187616</v>
       </c>
       <c r="B17" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>131187611</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>131187622</v>
       </c>
       <c r="B19" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131187613</v>
+        <v>131187621</v>
       </c>
       <c r="B20" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441028</v>
+        <v>441121</v>
       </c>
       <c r="R20" t="n">
-        <v>7056998</v>
+        <v>7056920</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131187621</v>
+        <v>131187613</v>
       </c>
       <c r="B21" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441121</v>
+        <v>441028</v>
       </c>
       <c r="R21" t="n">
-        <v>7056920</v>
+        <v>7056998</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
         <v>131187618</v>
       </c>
       <c r="B22" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>131187600</v>
       </c>
       <c r="B23" t="n">
-        <v>92543</v>
+        <v>92544</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -1681,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131187615</v>
+        <v>131187626</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>91842</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,23 +1692,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,10 +1712,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441121</v>
+        <v>441180</v>
       </c>
       <c r="R10" t="n">
-        <v>7057222</v>
+        <v>7057056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1752,11 +1748,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,7 +1774,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131187619</v>
+        <v>131187615</v>
       </c>
       <c r="B11" t="n">
         <v>57892</v>
@@ -1818,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441118</v>
+        <v>441121</v>
       </c>
       <c r="R11" t="n">
-        <v>7056975</v>
+        <v>7057222</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1885,7 +1876,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187614</v>
+        <v>131187619</v>
       </c>
       <c r="B12" t="n">
         <v>57892</v>
@@ -1920,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441097</v>
+        <v>441118</v>
       </c>
       <c r="R12" t="n">
-        <v>7057228</v>
+        <v>7056975</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1960,7 +1951,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187626</v>
+        <v>131187614</v>
       </c>
       <c r="B13" t="n">
-        <v>91842</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,19 +1989,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2018,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441180</v>
+        <v>441097</v>
       </c>
       <c r="R13" t="n">
-        <v>7057056</v>
+        <v>7057228</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,6 +2049,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 55660-2023 artfynd.xlsx
+++ b/artfynd/A 55660-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131154924</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>131154923</v>
       </c>
       <c r="B3" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>131154925</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>131154926</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131154933</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>131154932</v>
       </c>
       <c r="B7" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>131187612</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>131187623</v>
       </c>
       <c r="B9" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131187626</v>
+        <v>131187619</v>
       </c>
       <c r="B10" t="n">
-        <v>91842</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,19 +1692,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1712,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441180</v>
+        <v>441118</v>
       </c>
       <c r="R10" t="n">
-        <v>7057056</v>
+        <v>7056975</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,6 +1752,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131187615</v>
+        <v>131187614</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,10 +1818,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441121</v>
+        <v>441097</v>
       </c>
       <c r="R11" t="n">
-        <v>7057222</v>
+        <v>7057228</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,7 +1858,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,10 +1885,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131187619</v>
+        <v>131187626</v>
       </c>
       <c r="B12" t="n">
-        <v>57892</v>
+        <v>91848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,23 +1896,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1911,10 +1916,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441118</v>
+        <v>441180</v>
       </c>
       <c r="R12" t="n">
-        <v>7056975</v>
+        <v>7057056</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1947,11 +1952,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131187614</v>
+        <v>131187615</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441097</v>
+        <v>441121</v>
       </c>
       <c r="R13" t="n">
-        <v>7057228</v>
+        <v>7057222</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,7 +2083,7 @@
         <v>131187620</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>131187617</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131187625</v>
       </c>
       <c r="B16" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>131187616</v>
       </c>
       <c r="B17" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>131187611</v>
       </c>
       <c r="B18" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>131187622</v>
       </c>
       <c r="B19" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>131187621</v>
       </c>
       <c r="B20" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>131187613</v>
       </c>
       <c r="B21" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>131187618</v>
       </c>
       <c r="B22" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>131187600</v>
       </c>
       <c r="B23" t="n">
-        <v>92544</v>
+        <v>92550</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
